--- a/untranslated/downloads/data-excel/2.1.2.xlsx
+++ b/untranslated/downloads/data-excel/2.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E18A94F-04C2-4B12-B5F6-1FA3D61BC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10665" windowHeight="9360"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -190,17 +191,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="###0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,6 +342,18 @@
       <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman Cyr"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -386,146 +407,139 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="3" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="12">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="2"/>
-    <cellStyle name="Обычный 3" xfId="3"/>
-    <cellStyle name="Обычный 4" xfId="6"/>
-    <cellStyle name="Обычный_Лист2" xfId="7"/>
-    <cellStyle name="Процентный 2" xfId="5"/>
-    <cellStyle name="Процентный 3" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="11" xr:uid="{D63182F6-AF3B-43F8-B264-5FC8C624F7DB}"/>
+    <cellStyle name="Обычный 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 4 2" xfId="8" xr:uid="{768FFADE-C106-4578-9F54-EAA4422893CE}"/>
+    <cellStyle name="Обычный 5" xfId="9" xr:uid="{66D794F6-A671-4503-A475-D89A41C152CC}"/>
+    <cellStyle name="Обычный 6" xfId="10" xr:uid="{684AC96F-C6A3-4B14-ABAF-507B2B34FD86}"/>
+    <cellStyle name="Обычный_Лист2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Процентный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Процентный 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -541,9 +555,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -581,9 +595,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -618,7 +632,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -653,7 +667,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -826,8 +840,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" customWidth="1"/>
@@ -835,337 +849,372 @@
     <col min="3" max="3" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="37"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="10">
         <v>2019</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="10">
         <v>2020</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="10">
         <v>2021</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="34">
         <v>2022</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="34">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="I4" s="38">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="37"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="25">
         <v>4.5</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="25">
         <v>5.7</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="30">
         <v>7.6</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="30">
         <v>5.6522931163075061</v>
       </c>
-      <c r="H6" s="40">
+      <c r="H6" s="30">
         <v>4.684701603429354</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="I6" s="39">
+        <v>4.9662952837577308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="37"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="26">
         <v>6.9</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="26">
         <v>9.4</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="31">
         <v>12.9</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="31">
         <v>11.431224871295624</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="31">
         <v>9.1619177226137172</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="I8" s="40">
+        <v>9.9307093323270763</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="26">
         <v>3.1</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="26">
         <v>3.6</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="31">
         <v>4.5</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="31">
         <v>2.3014896328900498</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="31">
         <v>2.1026629736131146</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="I9" s="40">
+        <v>1.2425216414497104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-    </row>
-    <row r="11" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="40"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="26">
         <v>2.7</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="26">
         <v>2.4</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="33">
         <v>0.9</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="33">
         <v>1.135902336603809</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="33">
         <v>1.6883952033845095</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="40">
+        <v>2.247921706150902</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="26">
         <v>6.6</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="26">
         <v>7</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="31">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="31">
         <v>4.6416097340134757</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="31">
         <v>5.4628226647491029</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="40">
+        <v>4.9795884923806124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="26">
         <v>9.3000000000000007</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="31">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="31">
         <v>2.5190401033977778</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="31">
         <v>3.5472154122985047</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="40">
+        <v>0.51589291012468863</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="26">
         <v>1.8</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="26">
         <v>1.3</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="31">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="31">
         <v>4.87237654018735</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="31">
         <v>5.0893891878983322</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="40">
+        <v>7.564721828823509</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="26">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="26">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="31">
         <v>3.5</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="31">
         <v>1.0485236242224962</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="31">
         <v>0.47898402261907741</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="40">
+        <v>0.2040828106055316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="26">
         <v>3.3</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="26">
         <v>7.6</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="31">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="31">
         <v>8.3920504299407597</v>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="31">
         <v>6.7601470318978496</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="40">
+        <v>1.1066878282914432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -1175,356 +1224,393 @@
       <c r="C17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="26">
         <v>3</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="26">
         <v>4.2</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="31">
         <v>3.1</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="31">
         <v>4.496569224517259</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="31">
         <v>3.575054136227692</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="I17" s="40">
+        <v>2.5498768678919101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="26">
         <v>5.4</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="26">
         <v>10.3</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="31">
         <v>13.6</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="31">
         <v>11.111247880614005</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="31">
         <v>5.6091986107002105</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="I18" s="40">
+        <v>9.2021109373034484</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="26">
         <v>10.7</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="26">
         <v>12.2</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="31">
         <v>24.6</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="31">
         <v>24.120065334108446</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="31">
         <v>23.492624647686782</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="I19" s="40">
+        <v>21.299583209959984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="37"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="25">
         <v>0.8</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="25">
         <v>1.3</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="30">
         <v>1.6</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="30">
         <v>1.4897295269261084</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="30">
         <v>1.6110270246454947</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="I21" s="39">
+        <v>1.2762585927139607</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="37"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="26">
         <v>1.8</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="26">
         <v>2.9</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="31">
         <v>3.4</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="31">
         <v>3.1892622653075549</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="31">
         <v>3.5911978326282963</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="I23" s="40">
+        <v>2.7774547925104227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="26">
         <v>0.2</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="26">
         <v>0.4</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="31">
         <v>0.6</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="31">
         <v>0.50428784645720126</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="31">
         <v>0.46905009439682216</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="I24" s="40">
+        <v>0.15022140362293085</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="40"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="26">
         <v>0.1</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="26">
         <v>0</v>
       </c>
-      <c r="F26" s="43">
+      <c r="F26" s="33">
         <v>0.1</v>
       </c>
-      <c r="G26" s="43">
+      <c r="G26" s="33">
         <v>5.4126883056799469E-2</v>
       </c>
-      <c r="H26" s="43">
+      <c r="H26" s="33">
         <v>0.17806447072843995</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="40">
+        <v>0.24277707296534987</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="26">
         <v>2.1</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="26">
         <v>2.4</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="31">
         <v>3.2</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="31">
         <v>2.6203208437854411</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="31">
         <v>2.6322222213217694</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="40">
+        <v>2.9931303416237287</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="26">
         <v>0.7</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="26">
         <v>1.5</v>
       </c>
-      <c r="F28" s="41">
+      <c r="F28" s="31">
         <v>0.2</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="31">
         <v>0.40810394991406473</v>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="31">
         <v>1.8451824926932785</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="40">
+        <v>3.9090678909609787E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="26">
         <v>0.1</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="26">
         <v>0.4</v>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="31">
         <v>1.3</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="31">
         <v>0.83559945164153759</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="31">
         <v>0.59506627968271797</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="40">
+        <v>0.31620216328275458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="26">
         <v>0.1</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="26">
         <v>0.3</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="31">
         <v>0.7</v>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="31">
         <v>7.1735855281689909E-2</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="31">
         <v>2.8565820593621703E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="40">
+        <v>5.6373361434362237E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="26">
         <v>0.1</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="26">
         <v>0.8</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="31">
         <v>0.5</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="31">
         <v>1.1162300576418775</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="31">
         <v>0.17527311250618646</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="40">
+        <v>0.11039034473691736</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
@@ -1534,72 +1620,81 @@
       <c r="C32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D32" s="26">
         <v>0.7</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E32" s="26">
         <v>1.4</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="31">
         <v>0.5</v>
       </c>
-      <c r="G32" s="41">
+      <c r="G32" s="31">
         <v>1.528845742040833</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="31">
         <v>1.6783444058510675</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="I32" s="40">
+        <v>0.63337934936347318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="26">
         <v>0.4</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="26">
         <v>1.8</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="31">
         <v>0.9</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="31">
         <v>0.49548426668050499</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="31">
         <v>0.45739674737486102</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="I33" s="40">
+        <v>0.21102128461413233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="27">
         <v>2.7</v>
       </c>
-      <c r="E34" s="37">
+      <c r="E34" s="27">
         <v>3.7</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="27">
         <v>11.7</v>
       </c>
-      <c r="G34" s="46">
+      <c r="G34" s="36">
         <v>11.592242751251584</v>
       </c>
-      <c r="H34" s="46">
+      <c r="H34" s="36">
         <v>11.499084267608914</v>
+      </c>
+      <c r="I34" s="41">
+        <v>8.6621877839319321</v>
       </c>
     </row>
   </sheetData>
